--- a/research/traditional_assets/database/data/greece/greece_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_financial_svcs_non_bank_insurance.xlsx
@@ -588,124 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0203</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0902</v>
-      </c>
-      <c r="F2">
-        <v>0.51</v>
+        <v>0.368</v>
       </c>
       <c r="G2">
-        <v>0.2138974358974359</v>
+        <v>0.3632231404958678</v>
       </c>
       <c r="H2">
-        <v>0.1966666666666667</v>
+        <v>0.3415977961432507</v>
       </c>
       <c r="I2">
-        <v>0.2507692307692307</v>
+        <v>0.234435261707989</v>
       </c>
       <c r="J2">
-        <v>0.2229315455187015</v>
+        <v>0.181112731594015</v>
       </c>
       <c r="K2">
-        <v>9.67</v>
+        <v>7.88</v>
       </c>
       <c r="L2">
-        <v>0.247948717948718</v>
+        <v>0.2170798898071626</v>
       </c>
       <c r="M2">
-        <v>4.9</v>
+        <v>19.98</v>
       </c>
       <c r="N2">
-        <v>0.0192458758837392</v>
+        <v>0.1041167274622199</v>
       </c>
       <c r="O2">
-        <v>0.5067218200620476</v>
+        <v>2.535532994923858</v>
       </c>
       <c r="P2">
-        <v>4.9</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.0192458758837392</v>
+        <v>0.04627410109431996</v>
       </c>
       <c r="R2">
-        <v>0.5067218200620476</v>
+        <v>1.126903553299492</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="U2">
-        <v>79.7</v>
+        <v>60.7</v>
       </c>
       <c r="V2">
-        <v>0.3130400628436764</v>
+        <v>0.3163105784262637</v>
       </c>
       <c r="W2">
-        <v>0.08011599005799502</v>
+        <v>0.06380566801619433</v>
       </c>
       <c r="X2">
-        <v>0.02992082846257596</v>
+        <v>0.05794705966154562</v>
       </c>
       <c r="Y2">
-        <v>0.05019516159541906</v>
+        <v>0.005858608354648714</v>
       </c>
       <c r="Z2">
-        <v>0.8762666546835328</v>
+        <v>0.8262957820218069</v>
       </c>
       <c r="AA2">
-        <v>0.1953474796151023</v>
+        <v>0.1496526861865823</v>
       </c>
       <c r="AB2">
-        <v>0.0299265364936179</v>
+        <v>0.05795997908781662</v>
       </c>
       <c r="AC2">
-        <v>0.1654209431214844</v>
+        <v>0.09169270709876567</v>
       </c>
       <c r="AD2">
-        <v>0.131</v>
+        <v>0.187</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.131</v>
+        <v>0.187</v>
       </c>
       <c r="AG2">
-        <v>-79.569</v>
+        <v>-60.51300000000001</v>
       </c>
       <c r="AH2">
-        <v>0.0005142679925097456</v>
+        <v>0.0009735172083483004</v>
       </c>
       <c r="AI2">
-        <v>0.001059604791678463</v>
+        <v>0.001877755128681454</v>
       </c>
       <c r="AJ2">
-        <v>-0.4545994709508601</v>
+        <v>-0.4605706805087262</v>
       </c>
       <c r="AK2">
-        <v>-1.81122669641028</v>
+        <v>-1.556124154601795</v>
       </c>
       <c r="AL2">
-        <v>0.117</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AM2">
-        <v>-0.16</v>
+        <v>-0.3170000000000001</v>
       </c>
       <c r="AN2">
-        <v>0.01259615384615385</v>
+        <v>0.02052689352360044</v>
       </c>
       <c r="AO2">
-        <v>83.58974358974358</v>
+        <v>98.95348837209303</v>
       </c>
       <c r="AP2">
-        <v>-7.650865384615384</v>
+        <v>-6.642480790340286</v>
       </c>
       <c r="AQ2">
-        <v>-61.12499999999999</v>
+        <v>-26.84542586750788</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hellenic Exchanges - Athens Stock Exchange SA (ATSE:EXAE)</t>
+          <t>Hellenic Exchanges - Athens Stock Exchange S.A. (ATSE:EXAE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,124 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0203</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="E3">
-        <v>0.0902</v>
-      </c>
-      <c r="F3">
-        <v>0.51</v>
+        <v>0.368</v>
       </c>
       <c r="G3">
-        <v>0.2138974358974359</v>
+        <v>0.3632231404958678</v>
       </c>
       <c r="H3">
-        <v>0.1966666666666667</v>
+        <v>0.3415977961432507</v>
       </c>
       <c r="I3">
-        <v>0.2507692307692307</v>
+        <v>0.234435261707989</v>
       </c>
       <c r="J3">
-        <v>0.2229315455187015</v>
+        <v>0.181112731594015</v>
       </c>
       <c r="K3">
-        <v>9.67</v>
+        <v>7.88</v>
       </c>
       <c r="L3">
-        <v>0.247948717948718</v>
+        <v>0.2170798898071626</v>
       </c>
       <c r="M3">
-        <v>4.9</v>
+        <v>19.98</v>
       </c>
       <c r="N3">
-        <v>0.0192458758837392</v>
+        <v>0.1041167274622199</v>
       </c>
       <c r="O3">
-        <v>0.5067218200620476</v>
+        <v>2.535532994923858</v>
       </c>
       <c r="P3">
-        <v>4.9</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.0192458758837392</v>
+        <v>0.04627410109431996</v>
       </c>
       <c r="R3">
-        <v>0.5067218200620476</v>
+        <v>1.126903553299492</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="U3">
-        <v>79.7</v>
+        <v>60.7</v>
       </c>
       <c r="V3">
-        <v>0.3130400628436764</v>
+        <v>0.3163105784262637</v>
       </c>
       <c r="W3">
-        <v>0.08011599005799502</v>
+        <v>0.06380566801619433</v>
       </c>
       <c r="X3">
-        <v>0.02992082846257596</v>
+        <v>0.05794705966154562</v>
       </c>
       <c r="Y3">
-        <v>0.05019516159541906</v>
+        <v>0.005858608354648714</v>
       </c>
       <c r="Z3">
-        <v>0.8762666546835328</v>
+        <v>0.8262957820218069</v>
       </c>
       <c r="AA3">
-        <v>0.1953474796151023</v>
+        <v>0.1496526861865823</v>
       </c>
       <c r="AB3">
-        <v>0.0299265364936179</v>
+        <v>0.05795997908781662</v>
       </c>
       <c r="AC3">
-        <v>0.1654209431214844</v>
+        <v>0.09169270709876567</v>
       </c>
       <c r="AD3">
-        <v>0.131</v>
+        <v>0.187</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.131</v>
+        <v>0.187</v>
       </c>
       <c r="AG3">
-        <v>-79.569</v>
+        <v>-60.51300000000001</v>
       </c>
       <c r="AH3">
-        <v>0.0005142679925097456</v>
+        <v>0.0009735172083483004</v>
       </c>
       <c r="AI3">
-        <v>0.001059604791678463</v>
+        <v>0.001877755128681454</v>
       </c>
       <c r="AJ3">
-        <v>-0.4545994709508601</v>
+        <v>-0.4605706805087262</v>
       </c>
       <c r="AK3">
-        <v>-1.81122669641028</v>
+        <v>-1.556124154601795</v>
       </c>
       <c r="AL3">
-        <v>0.117</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AM3">
-        <v>-0.16</v>
+        <v>-0.3170000000000001</v>
       </c>
       <c r="AN3">
-        <v>0.01259615384615385</v>
+        <v>0.02052689352360044</v>
       </c>
       <c r="AO3">
-        <v>83.58974358974358</v>
+        <v>98.95348837209303</v>
       </c>
       <c r="AP3">
-        <v>-7.650865384615384</v>
+        <v>-6.642480790340286</v>
       </c>
       <c r="AQ3">
-        <v>-61.12499999999999</v>
+        <v>-26.84542586750788</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/greece/greece_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09080000000000001</v>
+        <v>0.03855</v>
       </c>
       <c r="E2">
-        <v>0.368</v>
+        <v>0.282</v>
+      </c>
+      <c r="F2">
+        <v>0.379</v>
       </c>
       <c r="G2">
-        <v>0.3632231404958678</v>
+        <v>0.1866347687400319</v>
       </c>
       <c r="H2">
-        <v>0.3415977961432507</v>
+        <v>0.1707814992025518</v>
       </c>
       <c r="I2">
-        <v>0.234435261707989</v>
+        <v>0.2062998405103668</v>
       </c>
       <c r="J2">
-        <v>0.181112731594015</v>
+        <v>0.1840776093681427</v>
       </c>
       <c r="K2">
-        <v>7.88</v>
+        <v>11.036</v>
       </c>
       <c r="L2">
-        <v>0.2170798898071626</v>
+        <v>0.1760127591706539</v>
       </c>
       <c r="M2">
-        <v>19.98</v>
+        <v>10.9</v>
       </c>
       <c r="N2">
-        <v>0.1041167274622199</v>
+        <v>0.03156218329231215</v>
       </c>
       <c r="O2">
-        <v>2.535532994923858</v>
+        <v>0.9876766944545126</v>
       </c>
       <c r="P2">
-        <v>8.880000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="Q2">
-        <v>0.04627410109431996</v>
+        <v>0.02773997393948169</v>
       </c>
       <c r="R2">
-        <v>1.126903553299492</v>
+        <v>0.8680681406306633</v>
       </c>
       <c r="S2">
-        <v>11.1</v>
+        <v>1.32</v>
       </c>
       <c r="T2">
-        <v>0.5555555555555556</v>
+        <v>0.1211009174311927</v>
       </c>
       <c r="U2">
-        <v>60.7</v>
+        <v>67</v>
       </c>
       <c r="V2">
-        <v>0.3163105784262637</v>
+        <v>0.1940060807876068</v>
       </c>
       <c r="W2">
-        <v>0.06380566801619433</v>
+        <v>0.04051057727580955</v>
       </c>
       <c r="X2">
-        <v>0.05794705966154562</v>
+        <v>0.07127313186539466</v>
       </c>
       <c r="Y2">
-        <v>0.005858608354648714</v>
+        <v>-0.03076255458958511</v>
       </c>
       <c r="Z2">
-        <v>0.8262957820218069</v>
+        <v>1.012482439000759</v>
       </c>
       <c r="AA2">
-        <v>0.1496526861865823</v>
+        <v>0.1274072774781479</v>
       </c>
       <c r="AB2">
-        <v>0.05795997908781662</v>
+        <v>0.06412003220279192</v>
       </c>
       <c r="AC2">
-        <v>0.09169270709876567</v>
+        <v>0.06328724527535601</v>
       </c>
       <c r="AD2">
-        <v>0.187</v>
+        <v>10.843</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.187</v>
+        <v>10.843</v>
       </c>
       <c r="AG2">
-        <v>-60.51300000000001</v>
+        <v>-56.157</v>
       </c>
       <c r="AH2">
-        <v>0.0009735172083483004</v>
+        <v>0.03044136184596553</v>
       </c>
       <c r="AI2">
-        <v>0.001877755128681454</v>
+        <v>0.07958574018481683</v>
       </c>
       <c r="AJ2">
-        <v>-0.4605706805087262</v>
+        <v>-0.1941851981202865</v>
       </c>
       <c r="AK2">
-        <v>-1.556124154601795</v>
+        <v>-0.8110133876348512</v>
       </c>
       <c r="AL2">
-        <v>0.08599999999999999</v>
+        <v>1.047</v>
       </c>
       <c r="AM2">
-        <v>-0.3170000000000001</v>
+        <v>0.1809999999999999</v>
       </c>
       <c r="AN2">
-        <v>0.02052689352360044</v>
+        <v>0.8937520606660073</v>
       </c>
       <c r="AO2">
-        <v>98.95348837209303</v>
+        <v>12.35434574976122</v>
       </c>
       <c r="AP2">
-        <v>-6.642480790340286</v>
+        <v>-4.628832838773492</v>
       </c>
       <c r="AQ2">
-        <v>-26.84542586750788</v>
+        <v>71.46408839779008</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +725,252 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09080000000000001</v>
+        <v>0.103</v>
       </c>
       <c r="E3">
-        <v>0.368</v>
+        <v>0.282</v>
+      </c>
+      <c r="F3">
+        <v>0.379</v>
       </c>
       <c r="G3">
-        <v>0.3632231404958678</v>
+        <v>0.2653089244851258</v>
       </c>
       <c r="H3">
-        <v>0.3415977961432507</v>
+        <v>0.2425629290617849</v>
       </c>
       <c r="I3">
-        <v>0.234435261707989</v>
+        <v>0.3020594965675057</v>
       </c>
       <c r="J3">
-        <v>0.181112731594015</v>
+        <v>0.2369849338841706</v>
       </c>
       <c r="K3">
-        <v>7.88</v>
+        <v>11.7</v>
       </c>
       <c r="L3">
-        <v>0.2170798898071626</v>
+        <v>0.2677345537757437</v>
       </c>
       <c r="M3">
-        <v>19.98</v>
+        <v>10.9</v>
       </c>
       <c r="N3">
-        <v>0.1041167274622199</v>
+        <v>0.03216287990557687</v>
       </c>
       <c r="O3">
-        <v>2.535532994923858</v>
+        <v>0.9316239316239318</v>
       </c>
       <c r="P3">
-        <v>8.880000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="Q3">
-        <v>0.04627410109431996</v>
+        <v>0.02826792564178224</v>
       </c>
       <c r="R3">
-        <v>1.126903553299492</v>
+        <v>0.8188034188034189</v>
       </c>
       <c r="S3">
-        <v>11.1</v>
+        <v>1.32</v>
       </c>
       <c r="T3">
-        <v>0.5555555555555556</v>
+        <v>0.1211009174311927</v>
       </c>
       <c r="U3">
-        <v>60.7</v>
+        <v>62.9</v>
       </c>
       <c r="V3">
-        <v>0.3163105784262637</v>
+        <v>0.1856004721156684</v>
       </c>
       <c r="W3">
-        <v>0.06380566801619433</v>
+        <v>0.1177062374245473</v>
       </c>
       <c r="X3">
-        <v>0.05794705966154562</v>
+        <v>0.05859715938978197</v>
       </c>
       <c r="Y3">
-        <v>0.005858608354648714</v>
+        <v>0.0591090780347653</v>
       </c>
       <c r="Z3">
-        <v>0.8262957820218069</v>
+        <v>1.123768868773626</v>
       </c>
       <c r="AA3">
-        <v>0.1496526861865823</v>
+        <v>0.266316291067407</v>
       </c>
       <c r="AB3">
-        <v>0.05795997908781662</v>
+        <v>0.05859559002993114</v>
       </c>
       <c r="AC3">
-        <v>0.09169270709876567</v>
+        <v>0.2077207010374758</v>
       </c>
       <c r="AD3">
-        <v>0.187</v>
+        <v>0.243</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.187</v>
+        <v>0.243</v>
       </c>
       <c r="AG3">
-        <v>-60.51300000000001</v>
+        <v>-62.657</v>
       </c>
       <c r="AH3">
-        <v>0.0009735172083483004</v>
+        <v>0.0007165119138534483</v>
       </c>
       <c r="AI3">
-        <v>0.001877755128681454</v>
+        <v>0.002263771275257819</v>
       </c>
       <c r="AJ3">
-        <v>-0.4605706805087262</v>
+        <v>-0.2268184171182618</v>
       </c>
       <c r="AK3">
-        <v>-1.556124154601795</v>
+        <v>-1.409828319420381</v>
       </c>
       <c r="AL3">
-        <v>0.08599999999999999</v>
+        <v>0.047</v>
       </c>
       <c r="AM3">
-        <v>-0.3170000000000001</v>
+        <v>-0.819</v>
       </c>
       <c r="AN3">
-        <v>0.02052689352360044</v>
+        <v>0.02076923076923077</v>
       </c>
       <c r="AO3">
-        <v>98.95348837209303</v>
+        <v>280.8510638297872</v>
       </c>
       <c r="AP3">
-        <v>-6.642480790340286</v>
+        <v>-5.355299145299146</v>
       </c>
       <c r="AQ3">
-        <v>-26.84542586750788</v>
+        <v>-16.11721611721612</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Haidemenos Integrated Printing Services S.A. (ATSE:HAIDE)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.0259</v>
+      </c>
+      <c r="G4">
+        <v>0.005684210526315789</v>
+      </c>
+      <c r="H4">
+        <v>0.005684210526315789</v>
+      </c>
+      <c r="I4">
+        <v>-0.01394736842105263</v>
+      </c>
+      <c r="J4">
+        <v>-0.01394736842105263</v>
+      </c>
+      <c r="K4">
+        <v>-0.664</v>
+      </c>
+      <c r="L4">
+        <v>-0.03494736842105264</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>4.1</v>
+      </c>
+      <c r="V4">
+        <v>0.6356589147286821</v>
+      </c>
+      <c r="W4">
+        <v>-0.03668508287292817</v>
+      </c>
+      <c r="X4">
+        <v>0.08394910434100736</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1206341872139355</v>
+      </c>
+      <c r="Z4">
+        <v>0.8246527777777777</v>
+      </c>
+      <c r="AA4">
+        <v>-0.01150173611111111</v>
+      </c>
+      <c r="AB4">
+        <v>0.06964447437565267</v>
+      </c>
+      <c r="AC4">
+        <v>-0.08114621048676378</v>
+      </c>
+      <c r="AD4">
+        <v>10.6</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>10.6</v>
+      </c>
+      <c r="AG4">
+        <v>6.5</v>
+      </c>
+      <c r="AH4">
+        <v>0.6217008797653959</v>
+      </c>
+      <c r="AI4">
+        <v>0.3667820069204152</v>
+      </c>
+      <c r="AJ4">
+        <v>0.5019305019305019</v>
+      </c>
+      <c r="AK4">
+        <v>0.2620967741935484</v>
+      </c>
+      <c r="AL4">
+        <v>1</v>
+      </c>
+      <c r="AM4">
+        <v>1</v>
+      </c>
+      <c r="AN4">
+        <v>24.53703703703704</v>
+      </c>
+      <c r="AO4">
+        <v>-0.265</v>
+      </c>
+      <c r="AP4">
+        <v>15.0462962962963</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.265</v>
       </c>
     </row>
   </sheetData>
